--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -118,8 +118,13 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D101">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(D2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E2:E101">
-    <cfRule type="containsBlanks" dxfId="0" priority="4">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
       <formula>LEN(TRIM(E2))=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -129,11 +134,11 @@
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" sqref="D2:D101">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showErrorMessage="1" sqref="D2:D101">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" sqref="E2:E101">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="E2:E101">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -130,15 +130,15 @@
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation showInputMessage="1" prompt="Full name of the employee." sqref="A2:A101"/>
-    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" error="Hire date must be on or after 2020-01-01." sqref="C2:C101">
+    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." sqref="C2:C101">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showErrorMessage="1" sqref="D2:D101">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." sqref="D2:D101">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="E2:E101">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="E2:E101">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -128,8 +128,13 @@
       <formula>LEN(TRIM(E2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation showInputMessage="1" prompt="Full name of the employee." sqref="A2:A101"/>
+  <dataValidations count="5">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Full name of the employee." sqref="A2:A101">
+      <formula1>LEN(TRIM(A2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B101">
+      <formula1>LEN(TRIM(B2))&gt;0</formula1>
+    </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." sqref="C2:C101">
       <formula1>43831</formula1>
       <formula2>47848</formula2>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -148,4 +148,16 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Name"/>
+    <column index="2" property="Email"/>
+    <column index="3" property="HireDate"/>
+    <column index="4" property="Salary"/>
+    <column index="5" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>